--- a/examples/sample_bill_核算.xlsx
+++ b/examples/sample_bill_核算.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,6 +465,21 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>核算材料费</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>核算人工费</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>核算措施费</t>
         </is>
       </c>
     </row>
@@ -502,18 +517,27 @@
         <v>2399.49</v>
       </c>
       <c r="G2" t="n">
+        <v>75000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>原清单报价</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>73016.48</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L2" t="n">
         <v>28721.9</v>
       </c>
-      <c r="I2" t="n">
+      <c r="M2" t="n">
         <v>10580.79</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>已核算 单价:人工11.97+材料30.43元/m² [细石混凝土找平层 30mm；细石混凝土垫层 40mm]</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/examples/sample_bill_核算.xlsx
+++ b/examples/sample_bill_核算.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="报价清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="报价清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,13 +531,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>73016.48</v>
+        <v>72257.42999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>28721.9</v>
+        <v>29831.46</v>
       </c>
       <c r="M2" t="n">
-        <v>10580.79</v>
+        <v>10617.24</v>
       </c>
     </row>
   </sheetData>

--- a/examples/sample_bill_核算.xlsx
+++ b/examples/sample_bill_核算.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,11 +475,6 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>核算人工费</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>核算措施费</t>
         </is>
       </c>
     </row>
@@ -536,9 +531,6 @@
       <c r="L2" t="n">
         <v>29831.46</v>
       </c>
-      <c r="M2" t="n">
-        <v>10617.24</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
